--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_shopMall.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_shopMall.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="121">
   <si>
     <t>id</t>
   </si>
@@ -176,6 +176,9 @@
     <t>积分</t>
   </si>
   <si>
+    <t>8#1</t>
+  </si>
+  <si>
     <t>防御卷轴</t>
   </si>
   <si>
@@ -197,7 +200,16 @@
     <t>10250001#98</t>
   </si>
   <si>
-    <t>耳环饰品箱子</t>
+    <t>艾利尼斯之殇</t>
+  </si>
+  <si>
+    <t>10250001#980</t>
+  </si>
+  <si>
+    <t>艾利尼斯之怒</t>
+  </si>
+  <si>
+    <t>10250001#1580</t>
   </si>
   <si>
     <t>炎狼兽(可交易)</t>
@@ -209,9 +221,6 @@
     <t>幸运宝石</t>
   </si>
   <si>
-    <t>10250001#980</t>
-  </si>
-  <si>
     <t>合成保护符咒</t>
   </si>
   <si>
@@ -306,6 +315,9 @@
   </si>
   <si>
     <t>荣誉戒指</t>
+  </si>
+  <si>
+    <t>暗黑之石</t>
   </si>
   <si>
     <t>炽炎魔的火种</t>
@@ -1121,19 +1133,19 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C6500"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1469,7 +1481,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.375" style="1"/>
@@ -1675,6 +1687,10 @@
       <c r="H5" s="1">
         <v>0</v>
       </c>
+      <c r="I5"/>
+      <c r="J5" t="s">
+        <v>44</v>
+      </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
@@ -1690,10 +1706,10 @@
         <v>101507199</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>43</v>
@@ -1706,6 +1722,10 @@
       </c>
       <c r="H6" s="1">
         <v>0</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6" t="s">
+        <v>44</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -1722,7 +1742,7 @@
         <v>101507299</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>42</v>
@@ -1738,6 +1758,10 @@
       </c>
       <c r="H7" s="1">
         <v>0</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7" t="s">
+        <v>44</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -1754,10 +1778,10 @@
         <v>101507399</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>43</v>
@@ -1786,10 +1810,10 @@
         <v>101507499</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>43</v>
@@ -1818,10 +1842,10 @@
         <v>100000009</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>43</v>
@@ -1844,16 +1868,16 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1">
-        <v>1031004</v>
+        <v>1031003</v>
       </c>
       <c r="B11" s="4">
-        <v>40011023</v>
+        <v>2120010199</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>43</v>
@@ -1876,16 +1900,16 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1">
-        <v>1031005</v>
-      </c>
-      <c r="B12" s="1">
-        <v>1160000399</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>52</v>
+        <v>1031004</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2120011199</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>43</v>
@@ -1908,16 +1932,16 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1">
-        <v>1031006</v>
+        <v>1031005</v>
       </c>
       <c r="B13" s="1">
-        <v>1254006799</v>
+        <v>1160000399</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>43</v>
@@ -1940,16 +1964,16 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1">
-        <v>1031008</v>
+        <v>1031006</v>
       </c>
       <c r="B14" s="1">
-        <v>1254003899</v>
+        <v>1254006799</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>43</v>
@@ -1972,16 +1996,16 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="1">
-        <v>1031009</v>
+        <v>1031008</v>
       </c>
       <c r="B15" s="1">
-        <v>1254004099</v>
+        <v>1254003899</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>43</v>
@@ -2004,16 +2028,16 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="1">
-        <v>1031010</v>
+        <v>1031009</v>
       </c>
       <c r="B16" s="1">
-        <v>1269000199</v>
+        <v>1254004099</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>43</v>
@@ -2036,16 +2060,16 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1">
-        <v>1031011</v>
+        <v>1031010</v>
       </c>
       <c r="B17" s="1">
-        <v>1270002999</v>
+        <v>1269000199</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>43</v>
@@ -2065,22 +2089,19 @@
       <c r="L17" s="1">
         <v>1</v>
       </c>
-      <c r="N17" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="1">
-        <v>1031012</v>
+        <v>1031011</v>
       </c>
       <c r="B18" s="1">
-        <v>200002999</v>
+        <v>1270002999</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>43</v>
@@ -2100,19 +2121,22 @@
       <c r="L18" s="1">
         <v>1</v>
       </c>
+      <c r="N18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="1">
-        <v>1031013</v>
+        <v>1031012</v>
       </c>
       <c r="B19" s="1">
-        <v>101404799</v>
+        <v>200002999</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>43</v>
@@ -2135,13 +2159,13 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="1">
-        <v>1031014</v>
+        <v>1031013</v>
       </c>
       <c r="B20" s="1">
-        <v>1254000299</v>
+        <v>101404799</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>66</v>
@@ -2167,16 +2191,16 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1">
-        <v>1031015</v>
+        <v>1031014</v>
       </c>
       <c r="B21" s="1">
-        <v>1254000199</v>
+        <v>1254000299</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>43</v>
@@ -2199,13 +2223,13 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="1">
-        <v>1031016</v>
+        <v>1031015</v>
       </c>
       <c r="B22" s="1">
-        <v>1269000299</v>
+        <v>1254000199</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>69</v>
@@ -2231,16 +2255,16 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1">
-        <v>1031017</v>
+        <v>1031016</v>
       </c>
       <c r="B23" s="1">
-        <v>1269000399</v>
+        <v>1269000299</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>43</v>
@@ -2263,22 +2287,22 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="1">
-        <v>1032016</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>71</v>
+        <v>1031017</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1269000399</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="E24" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F24" s="1">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -2295,16 +2319,16 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1">
-        <v>1032017</v>
+        <v>1032016</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>43</v>
@@ -2327,7 +2351,7 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="1">
-        <v>1032018</v>
+        <v>1032017</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>76</v>
@@ -2359,22 +2383,22 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1">
-        <v>3012003</v>
-      </c>
-      <c r="B27" s="1">
-        <v>100000002</v>
+        <v>1032018</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F27" s="1">
-        <v>3012</v>
+        <v>1032</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
@@ -2391,16 +2415,16 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="1">
-        <v>3012004</v>
+        <v>3012003</v>
       </c>
       <c r="B28" s="1">
-        <v>100000005</v>
+        <v>100000002</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>43</v>
@@ -2423,22 +2447,22 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1">
-        <v>3014020</v>
-      </c>
-      <c r="B29" s="4">
-        <v>1252000499</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>82</v>
+        <v>3012004</v>
+      </c>
+      <c r="B29" s="1">
+        <v>100000005</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F29" s="1">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -2455,16 +2479,16 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="1">
-        <v>3014021</v>
+        <v>3014020</v>
       </c>
       <c r="B30" s="4">
-        <v>1252000599</v>
+        <v>1252000499</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>43</v>
@@ -2487,16 +2511,16 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1">
-        <v>3014022</v>
+        <v>3014021</v>
       </c>
       <c r="B31" s="4">
-        <v>1252000699</v>
+        <v>1252000599</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>43</v>
@@ -2519,16 +2543,16 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="1">
-        <v>3014023</v>
+        <v>3014022</v>
       </c>
       <c r="B32" s="4">
-        <v>1252000799</v>
+        <v>1252000699</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>43</v>
@@ -2549,18 +2573,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>3014024</v>
+        <v>3014023</v>
       </c>
       <c r="B33" s="4">
-        <v>1252001299</v>
+        <v>1252000799</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>43</v>
@@ -2581,18 +2605,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>3014026</v>
+        <v>3014024</v>
       </c>
       <c r="B34" s="4">
-        <v>1252000999</v>
+        <v>1252001299</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>43</v>
@@ -2613,18 +2637,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" customFormat="1" spans="1:13">
       <c r="A35" s="1">
-        <v>3014027</v>
-      </c>
-      <c r="B35" s="4">
-        <v>1252001099</v>
+        <v>3014025</v>
+      </c>
+      <c r="B35" s="5">
+        <v>1252001399</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>43</v>
@@ -2638,25 +2662,28 @@
       <c r="H35" s="1">
         <v>0</v>
       </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="M35" s="1"/>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>3014028</v>
+        <v>3014026</v>
       </c>
       <c r="B36" s="4">
-        <v>1252001199</v>
+        <v>1252000999</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>43</v>
@@ -2674,6 +2701,70 @@
         <v>1</v>
       </c>
       <c r="L36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="1">
+        <v>3014027</v>
+      </c>
+      <c r="B37" s="4">
+        <v>1252001099</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="1">
+        <v>3014028</v>
+      </c>
+      <c r="B38" s="4">
+        <v>1252001199</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2682,59 +2773,65 @@
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="138"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" dxfId="1" priority="33" operator="greaterThan">
+    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="148"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
+    <cfRule type="duplicateValues" dxfId="0" priority="120"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A10">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13:A38">
+    <cfRule type="duplicateValues" dxfId="0" priority="263"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B9">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30:B38">
+    <cfRule type="cellIs" dxfId="2" priority="93" operator="greaterThan">
       <formula>2147483647</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
+  <conditionalFormatting sqref="A1:A4 A34:A38 A52:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="256"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A10">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12:A36">
-    <cfRule type="duplicateValues" dxfId="0" priority="238"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B9">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29:B36">
-    <cfRule type="cellIs" dxfId="1" priority="68" operator="greaterThan">
-      <formula>2147483647</formula>
-    </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A4 A33:A36 A52:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="231"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A4 A12:A36 A52:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
+  <conditionalFormatting sqref="A1:A4 A13:A38 A52:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B4 B52:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="157"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B4 B13:B15 B18:B27 B52:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="264"/>
+  <conditionalFormatting sqref="B1:B4 B14:B16 B19:B28 B52:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="289"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:B15 B18:B27">
-    <cfRule type="duplicateValues" dxfId="0" priority="275"/>
+  <conditionalFormatting sqref="B14:B16 B19:B28">
+    <cfRule type="duplicateValues" dxfId="0" priority="300"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -2756,10 +2853,10 @@
         <v>2140001599</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>43</v>
@@ -2788,10 +2885,10 @@
         <v>2140001699</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>43</v>
@@ -2820,10 +2917,10 @@
         <v>2140000799</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>43</v>
@@ -2852,10 +2949,10 @@
         <v>2140000899</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>43</v>
@@ -2884,10 +2981,10 @@
         <v>101509599</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>43</v>
@@ -2916,10 +3013,10 @@
         <v>101509699</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>43</v>
@@ -2948,10 +3045,10 @@
         <v>101611099</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>43</v>
@@ -2980,10 +3077,10 @@
         <v>101611199</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>43</v>
@@ -3012,10 +3109,10 @@
         <v>101611299</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>43</v>
@@ -3044,10 +3141,10 @@
         <v>101611399</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>43</v>
@@ -3076,10 +3173,10 @@
         <v>101611499</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>43</v>
@@ -3108,10 +3205,10 @@
         <v>101611599</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>43</v>
@@ -3140,10 +3237,10 @@
         <v>100000007</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>43</v>
@@ -3172,10 +3269,10 @@
         <v>60088888</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>43</v>
@@ -3204,13 +3301,13 @@
         <v>1160002399</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F15" s="1">
         <v>2011</v>
@@ -3222,7 +3319,7 @@
         <v>4</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
@@ -3242,13 +3339,13 @@
         <v>1231000299</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F16" s="1">
         <v>2012</v>
@@ -3260,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K16" s="1">
         <v>20</v>
@@ -3274,13 +3371,13 @@
         <v>1160002399</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F17" s="1">
         <v>2013</v>
@@ -3292,7 +3389,7 @@
         <v>4</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
@@ -3315,7 +3412,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A2">
@@ -3344,7 +3441,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B6">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-    <cfRule type="cellIs" dxfId="1" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="20" operator="greaterThan">
       <formula>2147483647</formula>
     </cfRule>
   </conditionalFormatting>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_shopMall.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_shopMall.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="备用" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$D$1:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$D$1:$D$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="144">
   <si>
     <t>id</t>
   </si>
@@ -200,25 +200,46 @@
     <t>10250001#98</t>
   </si>
   <si>
+    <t>还原宝石</t>
+  </si>
+  <si>
+    <t>10250001#680</t>
+  </si>
+  <si>
+    <t>大师天赋洗点果实</t>
+  </si>
+  <si>
+    <t>10250001#600</t>
+  </si>
+  <si>
     <t>艾利尼斯之殇</t>
   </si>
   <si>
+    <t>10250001#880</t>
+  </si>
+  <si>
+    <t>艾利尼斯之怒</t>
+  </si>
+  <si>
+    <t>10250001#1580</t>
+  </si>
+  <si>
+    <t>炎狼兽(可交易)</t>
+  </si>
+  <si>
+    <t>10250001#2800</t>
+  </si>
+  <si>
+    <t>幸运宝石</t>
+  </si>
+  <si>
     <t>10250001#980</t>
   </si>
   <si>
-    <t>艾利尼斯之怒</t>
-  </si>
-  <si>
-    <t>10250001#1580</t>
-  </si>
-  <si>
-    <t>炎狼兽(可交易)</t>
-  </si>
-  <si>
-    <t>10250001#2980</t>
-  </si>
-  <si>
-    <t>幸运宝石</t>
+    <t>光之石强化符文</t>
+  </si>
+  <si>
+    <t>10250001#380</t>
   </si>
   <si>
     <t>合成保护符咒</t>
@@ -230,81 +251,84 @@
     <t>洗点药水</t>
   </si>
   <si>
-    <t>10250001#600</t>
-  </si>
-  <si>
     <t>免罪符</t>
   </si>
   <si>
+    <t>10250001#180</t>
+  </si>
+  <si>
+    <t>恶魔广场自由入场券</t>
+  </si>
+  <si>
+    <t>10250001#100</t>
+  </si>
+  <si>
+    <t>血色城堡自由入场券</t>
+  </si>
+  <si>
+    <t>仓库扩展书</t>
+  </si>
+  <si>
+    <t>10250001#80</t>
+  </si>
+  <si>
+    <t>背包石</t>
+  </si>
+  <si>
+    <t>角色改名卡</t>
+  </si>
+  <si>
+    <t>10250001#480</t>
+  </si>
+  <si>
+    <t>战盟改名卡</t>
+  </si>
+  <si>
+    <t>60080001</t>
+  </si>
+  <si>
+    <t>魔剑士角色卡片</t>
+  </si>
+  <si>
+    <t>60080002</t>
+  </si>
+  <si>
+    <t>圣导师角色卡片</t>
+  </si>
+  <si>
+    <t>10250001#1280</t>
+  </si>
+  <si>
+    <t>60080003</t>
+  </si>
+  <si>
+    <t>召唤师角色卡片</t>
+  </si>
+  <si>
+    <t>10250001#2580</t>
+  </si>
+  <si>
+    <t>10250001#500</t>
+  </si>
+  <si>
+    <t>10250001#588</t>
+  </si>
+  <si>
+    <t>10250001#88</t>
+  </si>
+  <si>
+    <t>10250001#580</t>
+  </si>
+  <si>
+    <t>10250001#99</t>
+  </si>
+  <si>
+    <t>帝王之书</t>
+  </si>
+  <si>
     <t>10250001#50</t>
   </si>
   <si>
-    <t>恶魔广场自由入场券</t>
-  </si>
-  <si>
-    <t>10250001#100</t>
-  </si>
-  <si>
-    <t>血色城堡自由入场券</t>
-  </si>
-  <si>
-    <t>仓库扩展书</t>
-  </si>
-  <si>
-    <t>10250001#80</t>
-  </si>
-  <si>
-    <t>背包石</t>
-  </si>
-  <si>
-    <t>角色改名卡</t>
-  </si>
-  <si>
-    <t>10250001#480</t>
-  </si>
-  <si>
-    <t>战盟改名卡</t>
-  </si>
-  <si>
-    <t>60080001</t>
-  </si>
-  <si>
-    <t>魔剑士角色卡片</t>
-  </si>
-  <si>
-    <t>60080002</t>
-  </si>
-  <si>
-    <t>圣导师角色卡片</t>
-  </si>
-  <si>
-    <t>10250001#1280</t>
-  </si>
-  <si>
-    <t>60080003</t>
-  </si>
-  <si>
-    <t>召唤师角色卡片</t>
-  </si>
-  <si>
-    <t>10250001#2580</t>
-  </si>
-  <si>
-    <t>金币*100万</t>
-  </si>
-  <si>
-    <t>10250001#10</t>
-  </si>
-  <si>
-    <t>金币*1000万</t>
-  </si>
-  <si>
-    <t>帝王之书</t>
-  </si>
-  <si>
-    <t>10250001#5</t>
-  </si>
-  <si>
     <t>先知之魂</t>
   </si>
   <si>
@@ -323,13 +347,61 @@
     <t>炽炎魔的火种</t>
   </si>
   <si>
-    <t>10250001#20</t>
+    <t>10250001#200</t>
   </si>
   <si>
     <t>丛林召唤者的角</t>
   </si>
   <si>
     <t>天魔菲尼斯的羽毛</t>
+  </si>
+  <si>
+    <t>称号：叱咤风云</t>
+  </si>
+  <si>
+    <t>10040001#58</t>
+  </si>
+  <si>
+    <t>瑞币</t>
+  </si>
+  <si>
+    <t>称号：杀戮之王</t>
+  </si>
+  <si>
+    <t>10040001#128</t>
+  </si>
+  <si>
+    <t>称号：君临天下</t>
+  </si>
+  <si>
+    <t>10040001#328</t>
+  </si>
+  <si>
+    <t>称号：恶魔猎人</t>
+  </si>
+  <si>
+    <t>10040001#588</t>
+  </si>
+  <si>
+    <t>强化天使</t>
+  </si>
+  <si>
+    <t>10040001#1880</t>
+  </si>
+  <si>
+    <t>强化恶魔</t>
+  </si>
+  <si>
+    <t>奔雷战旗</t>
+  </si>
+  <si>
+    <t>10040001#2980</t>
+  </si>
+  <si>
+    <t>10040001#580</t>
+  </si>
+  <si>
+    <t>光明法师角色卡片</t>
   </si>
   <si>
     <t>强化恶魔(1天)</t>
@@ -366,6 +438,9 @@
     <t>幸运一击卷轴</t>
   </si>
   <si>
+    <t>10250001#20</t>
+  </si>
+  <si>
     <t>卓越一击卷轴</t>
   </si>
   <si>
@@ -391,12 +466,6 @@
   </si>
   <si>
     <t>金币*1亿</t>
-  </si>
-  <si>
-    <t>10250001#200</t>
-  </si>
-  <si>
-    <t>光明法师角色卡片</t>
   </si>
   <si>
     <t>10250001#188</t>
@@ -1049,7 +1118,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1068,6 +1137,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1481,7 +1556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.375" style="1"/>
@@ -1795,6 +1870,9 @@
       <c r="H8" s="1">
         <v>0</v>
       </c>
+      <c r="J8" t="s">
+        <v>44</v>
+      </c>
       <c r="K8" s="1">
         <v>1</v>
       </c>
@@ -1827,6 +1905,9 @@
       <c r="H9" s="1">
         <v>0</v>
       </c>
+      <c r="J9" t="s">
+        <v>44</v>
+      </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
@@ -1868,10 +1949,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="1">
-        <v>1031003</v>
+        <v>1031001</v>
       </c>
       <c r="B11" s="4">
-        <v>2120010199</v>
+        <v>1253001799</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>52</v>
@@ -1891,6 +1972,9 @@
       <c r="H11" s="1">
         <v>0</v>
       </c>
+      <c r="J11" t="s">
+        <v>44</v>
+      </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
@@ -1900,10 +1984,10 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="1">
-        <v>1031004</v>
+        <v>1031002</v>
       </c>
       <c r="B12" s="4">
-        <v>2120011199</v>
+        <v>31020002</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>54</v>
@@ -1923,6 +2007,9 @@
       <c r="H12" s="1">
         <v>0</v>
       </c>
+      <c r="J12" t="s">
+        <v>44</v>
+      </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
@@ -1932,12 +2019,12 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="1">
-        <v>1031005</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1160000399</v>
-      </c>
-      <c r="C13" s="1" t="s">
+        <v>1031003</v>
+      </c>
+      <c r="B13" s="4">
+        <v>2120010199</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1964,16 +2051,16 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1">
-        <v>1031006</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1254006799</v>
-      </c>
-      <c r="C14" s="1" t="s">
+        <v>1031004</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2120011199</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>43</v>
@@ -1996,16 +2083,16 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="1">
-        <v>1031008</v>
+        <v>1031005</v>
       </c>
       <c r="B15" s="1">
-        <v>1254003899</v>
+        <v>1160000399</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>43</v>
@@ -2028,16 +2115,16 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="1">
-        <v>1031009</v>
+        <v>1031006</v>
       </c>
       <c r="B16" s="1">
-        <v>1254004099</v>
+        <v>1254006799</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>43</v>
@@ -2051,6 +2138,9 @@
       <c r="H16" s="1">
         <v>0</v>
       </c>
+      <c r="J16" t="s">
+        <v>44</v>
+      </c>
       <c r="K16" s="1">
         <v>1</v>
       </c>
@@ -2060,16 +2150,16 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1">
-        <v>1031010</v>
-      </c>
-      <c r="B17" s="1">
-        <v>1269000199</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>61</v>
+        <v>1031007</v>
+      </c>
+      <c r="B17" s="4">
+        <v>210010399</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>43</v>
@@ -2083,6 +2173,9 @@
       <c r="H17" s="1">
         <v>0</v>
       </c>
+      <c r="J17" t="s">
+        <v>44</v>
+      </c>
       <c r="K17" s="1">
         <v>1</v>
       </c>
@@ -2092,16 +2185,16 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="1">
-        <v>1031011</v>
+        <v>1031008</v>
       </c>
       <c r="B18" s="1">
-        <v>1270002999</v>
+        <v>1254003899</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>43</v>
@@ -2115,28 +2208,28 @@
       <c r="H18" s="1">
         <v>0</v>
       </c>
+      <c r="J18" t="s">
+        <v>44</v>
+      </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1">
-        <v>1</v>
-      </c>
-      <c r="N18" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="1">
-        <v>1031012</v>
+        <v>1031009</v>
       </c>
       <c r="B19" s="1">
-        <v>200002999</v>
+        <v>1254004099</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>43</v>
@@ -2150,6 +2243,9 @@
       <c r="H19" s="1">
         <v>0</v>
       </c>
+      <c r="J19" t="s">
+        <v>44</v>
+      </c>
       <c r="K19" s="1">
         <v>1</v>
       </c>
@@ -2159,16 +2255,16 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="1">
-        <v>1031013</v>
+        <v>1031010</v>
       </c>
       <c r="B20" s="1">
-        <v>101404799</v>
+        <v>1269000199</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>43</v>
@@ -2182,6 +2278,9 @@
       <c r="H20" s="1">
         <v>0</v>
       </c>
+      <c r="J20" t="s">
+        <v>44</v>
+      </c>
       <c r="K20" s="1">
         <v>1</v>
       </c>
@@ -2191,16 +2290,16 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="1">
-        <v>1031014</v>
+        <v>1031011</v>
       </c>
       <c r="B21" s="1">
-        <v>1254000299</v>
+        <v>1270002999</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>43</v>
@@ -2214,25 +2313,31 @@
       <c r="H21" s="1">
         <v>0</v>
       </c>
+      <c r="J21" t="s">
+        <v>44</v>
+      </c>
       <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="N21" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="1">
-        <v>1031015</v>
+        <v>1031012</v>
       </c>
       <c r="B22" s="1">
-        <v>1254000199</v>
+        <v>200002999</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>43</v>
@@ -2246,6 +2351,9 @@
       <c r="H22" s="1">
         <v>0</v>
       </c>
+      <c r="J22" t="s">
+        <v>44</v>
+      </c>
       <c r="K22" s="1">
         <v>1</v>
       </c>
@@ -2255,13 +2363,13 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="1">
-        <v>1031016</v>
+        <v>1031013</v>
       </c>
       <c r="B23" s="1">
-        <v>1269000299</v>
+        <v>101404799</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>72</v>
@@ -2278,6 +2386,9 @@
       <c r="H23" s="1">
         <v>0</v>
       </c>
+      <c r="J23" t="s">
+        <v>44</v>
+      </c>
       <c r="K23" s="1">
         <v>1</v>
       </c>
@@ -2287,16 +2398,16 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="1">
-        <v>1031017</v>
+        <v>1031014</v>
       </c>
       <c r="B24" s="1">
-        <v>1269000399</v>
+        <v>1254000299</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>43</v>
@@ -2310,6 +2421,9 @@
       <c r="H24" s="1">
         <v>0</v>
       </c>
+      <c r="J24" t="s">
+        <v>44</v>
+      </c>
       <c r="K24" s="1">
         <v>1</v>
       </c>
@@ -2319,28 +2433,31 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="1">
-        <v>1032016</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>74</v>
+        <v>1031015</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1254000199</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E25" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F25" s="1">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>44</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
@@ -2351,10 +2468,10 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="1">
-        <v>1032017</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>76</v>
+        <v>1031016</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1269000299</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>77</v>
@@ -2366,13 +2483,16 @@
         <v>43</v>
       </c>
       <c r="F26" s="1">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>44</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
@@ -2383,28 +2503,31 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="1">
-        <v>1032018</v>
-      </c>
-      <c r="B27" s="1" t="s">
+        <v>1031017</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1269000399</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F27" s="1">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>44</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
@@ -2415,22 +2538,22 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="1">
-        <v>3012003</v>
-      </c>
-      <c r="B28" s="1">
-        <v>100000002</v>
+        <v>1032016</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F28" s="1">
-        <v>3012</v>
+        <v>1032</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
@@ -2447,22 +2570,22 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="1">
-        <v>3012004</v>
-      </c>
-      <c r="B29" s="1">
-        <v>100000005</v>
+        <v>1032017</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F29" s="1">
-        <v>3012</v>
+        <v>1032</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
@@ -2479,22 +2602,22 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="1">
-        <v>3014020</v>
-      </c>
-      <c r="B30" s="4">
-        <v>1252000499</v>
-      </c>
-      <c r="C30" s="4" t="s">
+        <v>1032018</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="C30" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="D30" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F30" s="1">
-        <v>3014</v>
+        <v>1032</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -2511,22 +2634,22 @@
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="1">
-        <v>3014021</v>
+        <v>3012003</v>
       </c>
       <c r="B31" s="4">
-        <v>1252000599</v>
+        <v>31020002</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F31" s="1">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -2543,22 +2666,22 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="1">
-        <v>3014022</v>
-      </c>
-      <c r="B32" s="4">
-        <v>1252000699</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>88</v>
+        <v>3012004</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1254006799</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F32" s="1">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -2575,22 +2698,22 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1">
-        <v>3014023</v>
-      </c>
-      <c r="B33" s="4">
-        <v>1252000799</v>
-      </c>
-      <c r="C33" s="4" t="s">
+        <v>3012005</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1269000199</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="E33" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F33" s="1">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -2607,22 +2730,22 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1">
-        <v>3014024</v>
-      </c>
-      <c r="B34" s="4">
-        <v>1252001299</v>
-      </c>
-      <c r="C34" s="4" t="s">
+        <v>3012006</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1270002999</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="E34" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F34" s="1">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -2637,24 +2760,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:13">
+    <row r="35" spans="1:13">
       <c r="A35" s="1">
-        <v>3014025</v>
-      </c>
-      <c r="B35" s="5">
-        <v>1252001399</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>91</v>
+        <v>3012007</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1269000299</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F35" s="1">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
@@ -2662,34 +2785,31 @@
       <c r="H35" s="1">
         <v>0</v>
       </c>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
         <v>1</v>
       </c>
-      <c r="M35" s="1"/>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1">
-        <v>3014026</v>
-      </c>
-      <c r="B36" s="4">
-        <v>1252000999</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>92</v>
+        <v>3012008</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1269000399</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F36" s="1">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -2706,22 +2826,22 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1">
-        <v>3014027</v>
-      </c>
-      <c r="B37" s="4">
-        <v>1252001099</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>94</v>
+        <v>3012009</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1254000199</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F37" s="1">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
@@ -2738,100 +2858,829 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1">
+        <v>3012010</v>
+      </c>
+      <c r="B38" s="1">
+        <v>200002999</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="1">
+        <v>3012</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="1">
+        <v>3012011</v>
+      </c>
+      <c r="B39" s="1">
+        <v>101404799</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="1">
+        <v>3012</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="1">
+        <v>3014020</v>
+      </c>
+      <c r="B40" s="4">
+        <v>1252000499</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="1">
+        <v>3014021</v>
+      </c>
+      <c r="B41" s="4">
+        <v>1252000599</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>1</v>
+      </c>
+      <c r="L41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="1">
+        <v>3014022</v>
+      </c>
+      <c r="B42" s="4">
+        <v>1252000699</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="1">
+        <v>3014023</v>
+      </c>
+      <c r="B43" s="4">
+        <v>1252000799</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="1">
+        <v>3014024</v>
+      </c>
+      <c r="B44" s="4">
+        <v>1252001299</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:13">
+      <c r="A45" s="1">
+        <v>3014025</v>
+      </c>
+      <c r="B45" s="5">
+        <v>1252001399</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1">
+        <v>1</v>
+      </c>
+      <c r="L45" s="1">
+        <v>1</v>
+      </c>
+      <c r="M45" s="1"/>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="1">
+        <v>3014026</v>
+      </c>
+      <c r="B46" s="4">
+        <v>1252000999</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F46" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="1">
+        <v>3014027</v>
+      </c>
+      <c r="B47" s="4">
+        <v>1252001099</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" s="1">
+        <v>3014</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="1">
         <v>3014028</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B48" s="4">
         <v>1252001199</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="1">
+      <c r="C48" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" s="1">
         <v>3014</v>
       </c>
-      <c r="G38" s="1">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="K38" s="1">
-        <v>1</v>
-      </c>
-      <c r="L38" s="1">
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="1">
+        <v>5001001</v>
+      </c>
+      <c r="B49" s="5">
+        <v>10101001</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F49" s="1">
+        <v>5001</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
+        <v>1</v>
+      </c>
+      <c r="L49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="1">
+        <v>5001002</v>
+      </c>
+      <c r="B50" s="5">
+        <v>10101002</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="1">
+        <v>5001</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="1">
+        <v>5001003</v>
+      </c>
+      <c r="B51" s="5">
+        <v>10101003</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F51" s="1">
+        <v>5001</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>1</v>
+      </c>
+      <c r="L51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="1">
+        <v>5001004</v>
+      </c>
+      <c r="B52" s="5">
+        <v>10101004</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F52" s="1">
+        <v>5001</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>1</v>
+      </c>
+      <c r="L52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="1">
+        <v>5002001</v>
+      </c>
+      <c r="B53" s="7">
+        <v>2140000899</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F53" s="1">
+        <v>5002</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1">
+        <v>1</v>
+      </c>
+      <c r="L53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="1">
+        <v>5002002</v>
+      </c>
+      <c r="B54" s="7">
+        <v>2140000799</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F54" s="1">
+        <v>5002</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="K54" s="1">
+        <v>1</v>
+      </c>
+      <c r="L54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="1">
+        <v>5002003</v>
+      </c>
+      <c r="B55" s="7">
+        <v>2000000199</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F55" s="1">
+        <v>5002</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1">
+        <v>1</v>
+      </c>
+      <c r="L55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="1">
+        <v>5002004</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1254003899</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F56" s="1">
+        <v>5003</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>1</v>
+      </c>
+      <c r="L56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="1">
+        <v>5002005</v>
+      </c>
+      <c r="B57" s="1">
+        <v>1254004099</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F57" s="1">
+        <v>5003</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>1</v>
+      </c>
+      <c r="L57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="1">
+        <v>5004001</v>
+      </c>
+      <c r="B58" s="5">
+        <v>1268000499</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F58" s="1">
+        <v>5004</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="D1:D51" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="D1:D66" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="0" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="1" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="132"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="0" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="130"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="1" priority="129"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="duplicateValues" dxfId="0" priority="264"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="120"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A10">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13:A38">
-    <cfRule type="duplicateValues" dxfId="0" priority="263"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B9">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B12">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30:B38">
-    <cfRule type="cellIs" dxfId="2" priority="93" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="108" operator="greaterThan">
       <formula>2147483647</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A4 A34:A38 A52:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="256"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A4 A13:A38 A52:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B4 B52:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="157"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B4 B14:B16 B19:B28 B52:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="289"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14:B16 B19:B28">
-    <cfRule type="duplicateValues" dxfId="0" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="180"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="1" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49">
+    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53">
+    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55">
+    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B56">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A10">
+    <cfRule type="duplicateValues" dxfId="0" priority="159"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34:A39">
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B9">
+    <cfRule type="duplicateValues" dxfId="0" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="141"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:B14">
+    <cfRule type="duplicateValues" dxfId="0" priority="128"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B36">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38:B39">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:B48">
+    <cfRule type="cellIs" dxfId="2" priority="209" operator="greaterThan">
+      <formula>2147483647</formula>
+    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="210"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50:B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C53:C54">
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEF9C"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A4 A44:A48 A67:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="372"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A4 A15:A16 A18:A32 A40:A48 A67:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="263"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B4 B67:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="273"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B4 B16 B18:B19 B22:B30 B67:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="405"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:A16 A18:A32 A40:A48">
+    <cfRule type="duplicateValues" dxfId="0" priority="379"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16 B18:B19 B22:B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="416"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -2853,10 +3702,10 @@
         <v>2140001599</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>43</v>
@@ -2885,10 +3734,10 @@
         <v>2140001699</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>43</v>
@@ -2917,10 +3766,10 @@
         <v>2140000799</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>43</v>
@@ -2949,10 +3798,10 @@
         <v>2140000899</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>43</v>
@@ -2981,10 +3830,10 @@
         <v>101509599</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>43</v>
@@ -3013,10 +3862,10 @@
         <v>101509699</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>43</v>
@@ -3045,10 +3894,10 @@
         <v>101611099</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>43</v>
@@ -3077,10 +3926,10 @@
         <v>101611199</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>43</v>
@@ -3109,10 +3958,10 @@
         <v>101611299</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>43</v>
@@ -3141,10 +3990,10 @@
         <v>101611399</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>43</v>
@@ -3173,10 +4022,10 @@
         <v>101611499</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>43</v>
@@ -3205,10 +4054,10 @@
         <v>101611599</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>43</v>
@@ -3237,10 +4086,10 @@
         <v>100000007</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>43</v>
@@ -3269,10 +4118,10 @@
         <v>60088888</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>43</v>
@@ -3301,13 +4150,13 @@
         <v>1160002399</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="F15" s="1">
         <v>2011</v>
@@ -3319,7 +4168,7 @@
         <v>4</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
@@ -3339,13 +4188,13 @@
         <v>1231000299</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="F16" s="1">
         <v>2012</v>
@@ -3357,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="K16" s="1">
         <v>20</v>
@@ -3371,13 +4220,13 @@
         <v>1160002399</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="F17" s="1">
         <v>2013</v>
@@ -3389,7 +4238,7 @@
         <v>4</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_shopMall.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_shopMall.xlsx
@@ -3,15 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\Out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="备用" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$D$1:$D$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$D$1:$D$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="154">
   <si>
     <t>id</t>
   </si>
@@ -230,87 +235,90 @@
     <t>10250001#2800</t>
   </si>
   <si>
+    <t>奔雷战旗(可交易)</t>
+  </si>
+  <si>
+    <t>光之石强化符文</t>
+  </si>
+  <si>
+    <t>10250001#380</t>
+  </si>
+  <si>
+    <t>合成保护符咒</t>
+  </si>
+  <si>
+    <t>10250001#980</t>
+  </si>
+  <si>
+    <t>幸运符咒</t>
+  </si>
+  <si>
+    <t>洗点药水</t>
+  </si>
+  <si>
+    <t>免罪符</t>
+  </si>
+  <si>
+    <t>10250001#180</t>
+  </si>
+  <si>
+    <t>恶魔广场自由入场券</t>
+  </si>
+  <si>
+    <t>10250001#100</t>
+  </si>
+  <si>
+    <t>血色城堡自由入场券</t>
+  </si>
+  <si>
+    <t>仓库扩展书</t>
+  </si>
+  <si>
+    <t>10250001#80</t>
+  </si>
+  <si>
+    <t>背包石</t>
+  </si>
+  <si>
+    <t>角色改名卡</t>
+  </si>
+  <si>
+    <t>10250001#480</t>
+  </si>
+  <si>
+    <t>战盟改名卡</t>
+  </si>
+  <si>
+    <t>60080001</t>
+  </si>
+  <si>
+    <t>魔剑士角色卡片</t>
+  </si>
+  <si>
+    <t>60080002</t>
+  </si>
+  <si>
+    <t>圣导师角色卡片</t>
+  </si>
+  <si>
+    <t>10250001#1280</t>
+  </si>
+  <si>
+    <t>60080003</t>
+  </si>
+  <si>
+    <t>召唤师角色卡片</t>
+  </si>
+  <si>
+    <t>10250001#2580</t>
+  </si>
+  <si>
+    <t>10250001#500</t>
+  </si>
+  <si>
     <t>幸运宝石</t>
   </si>
   <si>
-    <t>10250001#980</t>
-  </si>
-  <si>
-    <t>光之石强化符文</t>
-  </si>
-  <si>
-    <t>10250001#380</t>
-  </si>
-  <si>
-    <t>合成保护符咒</t>
-  </si>
-  <si>
-    <t>幸运符咒</t>
-  </si>
-  <si>
-    <t>洗点药水</t>
-  </si>
-  <si>
-    <t>免罪符</t>
-  </si>
-  <si>
-    <t>10250001#180</t>
-  </si>
-  <si>
-    <t>恶魔广场自由入场券</t>
-  </si>
-  <si>
-    <t>10250001#100</t>
-  </si>
-  <si>
-    <t>血色城堡自由入场券</t>
-  </si>
-  <si>
-    <t>仓库扩展书</t>
-  </si>
-  <si>
-    <t>10250001#80</t>
-  </si>
-  <si>
-    <t>背包石</t>
-  </si>
-  <si>
-    <t>角色改名卡</t>
-  </si>
-  <si>
-    <t>10250001#480</t>
-  </si>
-  <si>
-    <t>战盟改名卡</t>
-  </si>
-  <si>
-    <t>60080001</t>
-  </si>
-  <si>
-    <t>魔剑士角色卡片</t>
-  </si>
-  <si>
-    <t>60080002</t>
-  </si>
-  <si>
-    <t>圣导师角色卡片</t>
-  </si>
-  <si>
-    <t>10250001#1280</t>
-  </si>
-  <si>
-    <t>60080003</t>
-  </si>
-  <si>
-    <t>召唤师角色卡片</t>
-  </si>
-  <si>
-    <t>10250001#2580</t>
-  </si>
-  <si>
-    <t>10250001#500</t>
-  </si>
-  <si>
     <t>10250001#588</t>
   </si>
   <si>
@@ -356,52 +364,49 @@
     <t>天魔菲尼斯的羽毛</t>
   </si>
   <si>
-    <t>称号：叱咤风云</t>
-  </si>
-  <si>
-    <t>10040001#58</t>
+    <t>强化天使</t>
+  </si>
+  <si>
+    <t>10040001#3320</t>
   </si>
   <si>
     <t>瑞币</t>
   </si>
   <si>
-    <t>称号：杀戮之王</t>
-  </si>
-  <si>
-    <t>10040001#128</t>
-  </si>
-  <si>
-    <t>称号：君临天下</t>
-  </si>
-  <si>
-    <t>10040001#328</t>
-  </si>
-  <si>
-    <t>称号：恶魔猎人</t>
-  </si>
-  <si>
-    <t>10040001#588</t>
-  </si>
-  <si>
-    <t>强化天使</t>
-  </si>
-  <si>
-    <t>10040001#1880</t>
-  </si>
-  <si>
     <t>强化恶魔</t>
   </si>
   <si>
-    <t>奔雷战旗</t>
+    <t>10040001#180</t>
+  </si>
+  <si>
+    <t>10040001#980</t>
+  </si>
+  <si>
+    <t>10040001#1280</t>
+  </si>
+  <si>
+    <t>10040001#1580</t>
+  </si>
+  <si>
+    <t>光明法师角色卡片</t>
   </si>
   <si>
     <t>10040001#2980</t>
   </si>
   <si>
-    <t>10040001#580</t>
-  </si>
-  <si>
-    <t>光明法师角色卡片</t>
+    <t>大天使武器</t>
+  </si>
+  <si>
+    <t>10210001#18</t>
+  </si>
+  <si>
+    <t>大天使积分</t>
+  </si>
+  <si>
+    <t>大天使铁锤</t>
+  </si>
+  <si>
+    <t>10210001#8</t>
   </si>
   <si>
     <t>强化恶魔(1天)</t>
@@ -493,6 +498,36 @@
   </si>
   <si>
     <t>史诗猎魔坐骑（留着配表）</t>
+  </si>
+  <si>
+    <t>称号：叱咤风云</t>
+  </si>
+  <si>
+    <t>10040001#58</t>
+  </si>
+  <si>
+    <t>称号：杀戮之王</t>
+  </si>
+  <si>
+    <t>10040001#128</t>
+  </si>
+  <si>
+    <t>称号：君临天下</t>
+  </si>
+  <si>
+    <t>10040001#328</t>
+  </si>
+  <si>
+    <t>称号：恶魔猎人</t>
+  </si>
+  <si>
+    <t>10040001#588</t>
+  </si>
+  <si>
+    <t>奔雷战旗</t>
+  </si>
+  <si>
+    <t>10040001#580</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1153,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1135,14 +1170,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1556,7 +1594,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.375" style="1"/>
@@ -1624,7 +1662,7 @@
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1940,6 +1978,9 @@
       <c r="H10" s="1">
         <v>0</v>
       </c>
+      <c r="J10" t="s">
+        <v>44</v>
+      </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
@@ -2042,6 +2083,9 @@
       <c r="H13" s="1">
         <v>0</v>
       </c>
+      <c r="J13" t="s">
+        <v>44</v>
+      </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
@@ -2074,6 +2118,9 @@
       <c r="H14" s="1">
         <v>0</v>
       </c>
+      <c r="J14" t="s">
+        <v>44</v>
+      </c>
       <c r="K14" s="1">
         <v>1</v>
       </c>
@@ -2118,13 +2165,13 @@
         <v>1031006</v>
       </c>
       <c r="B16" s="1">
-        <v>1254006799</v>
-      </c>
-      <c r="C16" s="1" t="s">
+        <v>2000000199</v>
+      </c>
+      <c r="C16" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>43</v>
@@ -2138,9 +2185,7 @@
       <c r="H16" s="1">
         <v>0</v>
       </c>
-      <c r="J16" t="s">
-        <v>44</v>
-      </c>
+      <c r="J16"/>
       <c r="K16" s="1">
         <v>1</v>
       </c>
@@ -2156,10 +2201,10 @@
         <v>210010399</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>43</v>
@@ -2191,10 +2236,10 @@
         <v>1254003899</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>43</v>
@@ -2229,7 +2274,7 @@
         <v>67</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>43</v>
@@ -2547,7 +2592,7 @@
         <v>81</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>43</v>
@@ -2560,6 +2605,9 @@
       </c>
       <c r="H28" s="1">
         <v>0</v>
+      </c>
+      <c r="J28" t="s">
+        <v>44</v>
       </c>
       <c r="K28" s="1">
         <v>1</v>
@@ -2593,6 +2641,9 @@
       <c r="H29" s="1">
         <v>0</v>
       </c>
+      <c r="J29" t="s">
+        <v>44</v>
+      </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
@@ -2625,6 +2676,9 @@
       <c r="H30" s="1">
         <v>0</v>
       </c>
+      <c r="J30" t="s">
+        <v>44</v>
+      </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
@@ -2672,7 +2726,7 @@
         <v>1254006799</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>57</v>
@@ -2707,7 +2761,7 @@
         <v>68</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>43</v>
@@ -2733,13 +2787,13 @@
         <v>3012006</v>
       </c>
       <c r="B34" s="1">
-        <v>1270002999</v>
+        <v>100000009</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>43</v>
@@ -2771,7 +2825,7 @@
         <v>77</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>43</v>
@@ -2803,7 +2857,7 @@
         <v>79</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>43</v>
@@ -2835,7 +2889,7 @@
         <v>76</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>43</v>
@@ -2867,7 +2921,7 @@
         <v>71</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>43</v>
@@ -2899,7 +2953,7 @@
         <v>73</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>43</v>
@@ -2928,10 +2982,10 @@
         <v>1252000499</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>43</v>
@@ -2960,10 +3014,10 @@
         <v>1252000599</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>43</v>
@@ -2992,10 +3046,10 @@
         <v>1252000699</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>43</v>
@@ -3024,10 +3078,10 @@
         <v>1252000799</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>43</v>
@@ -3056,7 +3110,7 @@
         <v>1252001299</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>72</v>
@@ -3088,7 +3142,7 @@
         <v>1252001399</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>72</v>
@@ -3123,10 +3177,10 @@
         <v>1252000999</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>43</v>
@@ -3155,10 +3209,10 @@
         <v>1252001099</v>
       </c>
       <c r="C47" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>43</v>
@@ -3187,10 +3241,10 @@
         <v>1252001199</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>43</v>
@@ -3215,17 +3269,17 @@
       <c r="A49" s="1">
         <v>5001001</v>
       </c>
-      <c r="B49" s="5">
-        <v>10101001</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>104</v>
+      <c r="B49" s="6">
+        <v>2140000899</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>105</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F49" s="1">
         <v>5001</v>
@@ -3247,17 +3301,17 @@
       <c r="A50" s="1">
         <v>5001002</v>
       </c>
-      <c r="B50" s="5">
-        <v>10101002</v>
-      </c>
-      <c r="C50" s="4" t="s">
+      <c r="B50" s="6">
+        <v>2140000799</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="F50" s="1">
         <v>5001</v>
@@ -3279,17 +3333,17 @@
       <c r="A51" s="1">
         <v>5001003</v>
       </c>
-      <c r="B51" s="5">
-        <v>10101003</v>
-      </c>
-      <c r="C51" s="4" t="s">
+      <c r="B51" s="1">
+        <v>1270002999</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F51" s="1">
         <v>5001</v>
@@ -3309,22 +3363,22 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="1">
-        <v>5001004</v>
-      </c>
-      <c r="B52" s="5">
-        <v>10101004</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>111</v>
+        <v>5002001</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F52" s="1">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
@@ -3341,19 +3395,19 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="1">
-        <v>5002001</v>
-      </c>
-      <c r="B53" s="7">
-        <v>2140000899</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>113</v>
+        <v>5002002</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F53" s="1">
         <v>5002</v>
@@ -3373,19 +3427,19 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="1">
-        <v>5002002</v>
-      </c>
-      <c r="B54" s="7">
-        <v>2140000799</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>115</v>
+        <v>5002003</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F54" s="1">
         <v>5002</v>
@@ -3405,19 +3459,19 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="1">
-        <v>5002003</v>
-      </c>
-      <c r="B55" s="7">
-        <v>2000000199</v>
+        <v>5002004</v>
+      </c>
+      <c r="B55" s="5">
+        <v>1268000499</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F55" s="1">
         <v>5002</v>
@@ -3437,22 +3491,22 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="1">
-        <v>5002004</v>
+        <v>6001001</v>
       </c>
       <c r="B56" s="1">
-        <v>1254003899</v>
+        <v>1019199</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F56" s="1">
-        <v>5003</v>
+        <v>6001</v>
       </c>
       <c r="G56" s="1">
         <v>0</v>
@@ -3469,22 +3523,22 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="1">
-        <v>5002005</v>
+        <v>6001002</v>
       </c>
       <c r="B57" s="1">
-        <v>1254004099</v>
+        <v>1124199</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F57" s="1">
-        <v>5003</v>
+        <v>6001</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
@@ -3501,161 +3555,276 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="1">
-        <v>5004001</v>
-      </c>
-      <c r="B58" s="5">
-        <v>1268000499</v>
-      </c>
-      <c r="C58" s="4" t="s">
+        <v>6001003</v>
+      </c>
+      <c r="B58" s="1">
+        <v>1098199</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F58" s="1">
+        <v>6001</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="1">
+        <v>6001004</v>
+      </c>
+      <c r="B59" s="1">
+        <v>1144199</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F59" s="1">
+        <v>6001</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="K59" s="1">
+        <v>1</v>
+      </c>
+      <c r="L59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="1">
+        <v>6001005</v>
+      </c>
+      <c r="B60" s="1">
+        <v>1058199</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F60" s="1">
+        <v>6001</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>1</v>
+      </c>
+      <c r="L60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="1">
+        <v>6003001</v>
+      </c>
+      <c r="B61" s="1">
+        <v>1254003799</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F58" s="1">
-        <v>5004</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
-      </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <v>1</v>
-      </c>
-      <c r="L58" s="1">
+      <c r="F61" s="1">
+        <v>6003</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" s="1">
+        <v>1</v>
+      </c>
+      <c r="L61" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="D1:D66" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="D1:D61" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="0" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="0" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="153"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="150"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="0" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13">
-    <cfRule type="duplicateValues" dxfId="1" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="167"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="1" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="0" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="301"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17">
-    <cfRule type="cellIs" dxfId="2" priority="108" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="145" operator="greaterThan">
       <formula>2147483647</formula>
     </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="144"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="duplicateValues" dxfId="0" priority="218"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="duplicateValues" dxfId="0" priority="217"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="1" priority="108"/>
     <cfRule type="duplicateValues" dxfId="0" priority="107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="0" priority="180"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="1" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33">
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B49">
     <cfRule type="duplicateValues" dxfId="0" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34">
+    <cfRule type="duplicateValues" dxfId="1" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B50">
     <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
-    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53">
-    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B54">
-    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B55">
-    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B56">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B57">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D56">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D57">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D58">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D59">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D60">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="D61">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:A10">
-    <cfRule type="duplicateValues" dxfId="0" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34:A39">
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B9">
-    <cfRule type="duplicateValues" dxfId="0" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:B12">
-    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="152"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35:B36">
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:B39">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40:B48">
-    <cfRule type="cellIs" dxfId="2" priority="209" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="246" operator="greaterThan">
       <formula>2147483647</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="0" priority="210"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B50:B52">
-    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="81"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C53:C54">
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-    <cfRule type="colorScale" priority="9">
+    <cfRule type="duplicateValues" dxfId="0" priority="247"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52:B54">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59:B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C49:C50">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -3663,24 +3832,26 @@
         <color rgb="FFFFEF9C"/>
       </colorScale>
     </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A4 A15:A16 A18:A32 A40:A48 A67:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="300"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:A4 A44:A48 A67:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="372"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A4 A15:A16 A18:A32 A40:A48 A67:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="263"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B4 B67:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="273"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B4 B16 B18:B19 B22:B30 B67:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="409"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B4 B16 B18:B19 B22:B30 B62:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="442"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B4 B62:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="310"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A16 A18:A32 A40:A48">
-    <cfRule type="duplicateValues" dxfId="0" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16 B18:B19 B22:B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="453"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -3691,7 +3862,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="16.5" spans="1:13">
@@ -4089,7 +4260,7 @@
         <v>134</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>43</v>
@@ -4118,7 +4289,7 @@
         <v>60088888</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>135</v>
@@ -4250,54 +4421,296 @@
         <v>2</v>
       </c>
     </row>
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A18" s="1">
+        <v>5001001</v>
+      </c>
+      <c r="B18" s="5">
+        <v>10101001</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="1">
+        <v>5001</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A19" s="1">
+        <v>5001002</v>
+      </c>
+      <c r="B19" s="5">
+        <v>10101002</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5001</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A20" s="1">
+        <v>5001003</v>
+      </c>
+      <c r="B20" s="5">
+        <v>10101003</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5001</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A21" s="1">
+        <v>5001004</v>
+      </c>
+      <c r="B21" s="5">
+        <v>10101004</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="1">
+        <v>5001</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A22" s="1">
+        <v>5002003</v>
+      </c>
+      <c r="B22" s="6">
+        <v>2000000199</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5002</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A23" s="1">
+        <v>5002004</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1254003899</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="1">
+        <v>5003</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A24" s="1">
+        <v>5002005</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1254004099</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5003</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
     <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
+  <conditionalFormatting sqref="B18">
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A2">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A4">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A4">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A6">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:A12">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15:A17">
     <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A2">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A4">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A4">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A6">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A12">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:A17">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B2">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B6">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-    <cfRule type="cellIs" dxfId="2" priority="20" operator="greaterThan">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+    <cfRule type="cellIs" dxfId="2" priority="28" operator="greaterThan">
       <formula>2147483647</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B12">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:B17">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19 B20 B21">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
